--- a/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
+++ b/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
@@ -563,6 +563,36 @@
           <t>Changed To</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Changed To</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Changed To</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Changed To</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">

--- a/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
+++ b/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Linko DB Monthly Quality Check  —  June 02, 2026</t>
+          <t>Linko DB Monthly Quality Check  —  June 03, 2026</t>
         </is>
       </c>
     </row>
@@ -688,11 +688,7 @@
           <t>120</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>EX120 - EX129</t>
-        </is>
-      </c>
+      <c r="E7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="inlineStr"/>
@@ -734,11 +730,7 @@
           <t>050</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>EX050</t>
-        </is>
-      </c>
+      <c r="E9" s="8" t="inlineStr"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="9" t="inlineStr"/>
@@ -872,11 +864,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>EX200 - EX220</t>
-        </is>
-      </c>
+      <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
           <t>20 gal</t>
@@ -905,11 +893,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>EX200 - EX220</t>
-        </is>
-      </c>
+      <c r="E16" s="8" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="9" t="inlineStr"/>
@@ -951,11 +935,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>EX200 - EX220</t>
-        </is>
-      </c>
+      <c r="E18" s="8" t="inlineStr"/>
       <c r="F18" s="8" t="inlineStr">
         <is>
           <t>50 gal</t>
@@ -1046,11 +1026,7 @@
           <t>Twice Monthly</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
+      <c r="I21" s="8" t="inlineStr"/>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="9" t="inlineStr"/>
@@ -1115,11 +1091,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>EX200 - EX220</t>
-        </is>
-      </c>
+      <c r="E24" s="8" t="inlineStr"/>
       <c r="F24" s="8" t="inlineStr">
         <is>
           <t>40 gal</t>
@@ -1255,11 +1227,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>EX200 - EX220</t>
-        </is>
-      </c>
+      <c r="E30" s="8" t="inlineStr"/>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="9" t="inlineStr"/>
@@ -1366,11 +1334,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>EX200 - EX220</t>
-        </is>
-      </c>
+      <c r="E35" s="8" t="inlineStr"/>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="9" t="inlineStr"/>
@@ -1431,11 +1395,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>EX200 - EX220</t>
-        </is>
-      </c>
+      <c r="E38" s="8" t="inlineStr"/>
       <c r="F38" s="8" t="inlineStr">
         <is>
           <t>20 lbs</t>
@@ -1613,146 +1573,294 @@
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Report Name:</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Master List with Additional Fields</t>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Care</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>9922</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Aqua Indiana</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="9" t="inlineStr"/>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Ziano's</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>9973</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Aqua Indiana</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="9" t="inlineStr"/>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Tiffany Nails Inc.</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>17657</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Salon (No Food)</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>Salon (No food)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Fields Checked:</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>MapCategory</t>
+      <c r="A51" s="9" t="inlineStr"/>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>17732</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Distillery (No Food)</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Distillery (No food)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Issues Found:</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Report Name:</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>AG Extract Summary</t>
+      <c r="A52" s="9" t="inlineStr"/>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Royalty Nails Lounge</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>17765</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Salon (No Food)</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>Salon (No food)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="9" t="inlineStr"/>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Gratitude Catering</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>17779</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Aqua Indiana</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="9" t="inlineStr"/>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>M. Vince Nail Spa</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>17861</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Salon (No Food)</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>Salon (No food)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Fields Checked:</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Extractor ID,  Extractor Type</t>
+      <c r="A55" s="9" t="inlineStr"/>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Dupont Sports and Medicine Complex</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>17939</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Blank</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Issues Found:</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Report Name:</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Inspection Events</t>
-        </is>
-      </c>
+      <c r="A56" s="9" t="inlineStr"/>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Let's Get Nailed</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>17971</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Salon (No Food)</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>Salon (No food)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="9" t="inlineStr"/>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Tocho Snack Bar</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>18018</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Aqua Indiana</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="9" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Board &amp; Bond</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>18034</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Aqua Indiana</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr"/>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Fields Checked:</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>EventTypeAbbrv</t>
-        </is>
-      </c>
+      <c r="A59" s="9" t="inlineStr"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Taco Rancho Grande</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>18036</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Aqua Indiana</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr"/>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Issues Found:</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Allen County Community Corrections Residential Services Facillity</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>17854</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr"/>
+      <c r="A60" s="9" t="inlineStr"/>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Hatfield &amp; Sons Distillery</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>18157</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>Distillery (No Food)</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>Distillery (No food)</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="9" t="inlineStr"/>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Bubba's 33</t>
+          <t>El Rey del Pincho FT</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Aqua Indiana</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr"/>
@@ -1761,17 +1869,17 @@
       <c r="A62" s="9" t="inlineStr"/>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Crispy Cones</t>
+          <t>The Flavor Patch FT</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Aqua Indiana</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr"/>
@@ -1780,112 +1888,87 @@
       <c r="A63" s="9" t="inlineStr"/>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Drive &amp; Shine Car Wash</t>
+          <t>Cooking With Herbs Catering LLC</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Aqua Indiana</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr"/>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="9" t="inlineStr"/>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Drive &amp; Shine Lube Center</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>18467</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr"/>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="9" t="inlineStr"/>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Dunkin Donuts #346590</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>10211</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr"/>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="9" t="inlineStr"/>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Headwaters Church</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>9392</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr"/>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Queen Nails</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>18400</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Salon (No Food)</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>Salon (No food)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Report Name:</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Master List with Additional Fields</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="9" t="inlineStr"/>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Hoshi Hoshi</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>18463</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Fields Checked:</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>MapCategory</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="9" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Issues Found:</t>
+        </is>
+      </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Mi Tierra Market</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr"/>
@@ -1894,17 +1977,17 @@
       <c r="A69" s="9" t="inlineStr"/>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Rise N Roll Bakery &amp; Deli</t>
+          <t>Divert Inc.</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>0067</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr"/>
@@ -1913,17 +1996,17 @@
       <c r="A70" s="9" t="inlineStr"/>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Thai Diner Restaurant</t>
+          <t>Drumm Inc.</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr"/>
@@ -1932,17 +2015,17 @@
       <c r="A71" s="9" t="inlineStr"/>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>The Grind</t>
+          <t>Proctor &amp; Gamble Lima</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr"/>
@@ -1951,17 +2034,17 @@
       <c r="A72" s="9" t="inlineStr"/>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Valvoline</t>
+          <t>Emery</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr"/>
@@ -1970,17 +2053,17 @@
       <c r="A73" s="9" t="inlineStr"/>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Van Eerden Food Service</t>
+          <t>Clean City Bins</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Dye Trace Monitoring Point</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr"/>
@@ -1989,39 +2072,388 @@
       <c r="A74" s="9" t="inlineStr"/>
       <c r="B74" s="6" t="inlineStr">
         <is>
+          <t>Dannon Co.</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>18460</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Quasar</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Report Name:</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>AG Extract Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Fields Checked:</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Extractor ID,  Extractor Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Issues Found:</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Report Name:</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Inspection Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Fields Checked:</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>EventTypeAbbrv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Issues Found:</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Allen County Community Corrections Residential Services Facillity</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>17854</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr"/>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="9" t="inlineStr"/>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Bubba's 33</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>18459</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr"/>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="9" t="inlineStr"/>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Crispy Cones</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>18449</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr"/>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="9" t="inlineStr"/>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Drive &amp; Shine Car Wash</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>18465</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr"/>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="9" t="inlineStr"/>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Drive &amp; Shine Lube Center</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>18467</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr"/>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="9" t="inlineStr"/>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Dunkin Donuts #346590</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>10211</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="9" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Headwaters Church</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>9392</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr"/>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="9" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Hoshi Hoshi</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>18463</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr"/>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="9" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Mi Tierra Market</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>18458</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr"/>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="9" t="inlineStr"/>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Rise N Roll Bakery &amp; Deli</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>0067</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="9" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Thai Diner Restaurant</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr"/>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="9" t="inlineStr"/>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>The Grind</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>9777</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr"/>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="9" t="inlineStr"/>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Valvoline</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>18423</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr"/>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="9" t="inlineStr"/>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Van Eerden Food Service</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>18441</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr"/>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="9" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
           <t>Wing Stop</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>17897</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr"/>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="9" t="inlineStr"/>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr"/>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="9" t="inlineStr"/>
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>YWCA/Gratitude Catering</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>9269</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr"/>
+      <c r="E97" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
+++ b/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
@@ -2182,11 +2182,7 @@
           <t>.</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>Blank</t>
-        </is>
-      </c>
+      <c r="F62" s="9" t="inlineStr"/>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="11" t="inlineStr"/>

--- a/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
+++ b/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
@@ -34,18 +34,18 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
-      <color rgb="000070C0"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
       <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="000070C0"/>
       <sz val="11"/>
     </font>
     <font>
@@ -74,7 +74,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="0092D050"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,7 +84,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0092D050"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -122,22 +122,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,16 +155,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -526,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,2749 +550,2782 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Color Key:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Auto-fixed — the tool applied a clear correction (casing, EX prefix, trap unit). Apply it as-is in Linko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Needs review — no certain fix; a person must decide (old extractor IDs, unknown values, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>Report Name:</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Permit List – Extractors</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Permit No</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Changed To</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Fields Checked:</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Extractor ID,  Extractor Type,  Trap Size &amp; Units,  Cleaning Frequency</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>American Kolache</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>18443</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="11" t="inlineStr"/>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="13" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Arby's #1201</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>6052</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="11" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="13" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>B. Antonio's Pizza</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>9893</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="11" t="inlineStr"/>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="13" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Bowen Coffee Shop</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>18488</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>EX120</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="11" t="inlineStr"/>
-      <c r="B8" s="12" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="13" t="inlineStr"/>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Buffalo Wild Wings</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>8071</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="11" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="13" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Burger Bar</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>18462</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>050</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="11" t="inlineStr"/>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Chick-fil-A #03479</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>17663</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="11" t="inlineStr"/>
-      <c r="B11" s="12" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="13" t="inlineStr"/>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Chicken Salad Chick</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>18130</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="11" t="inlineStr"/>
-      <c r="B12" s="12" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>9322</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="11" t="inlineStr"/>
-      <c r="B13" s="12" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="13" t="inlineStr"/>
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>9727</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="11" t="inlineStr"/>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Club Soda</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>9042</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>EX001</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="11" t="inlineStr"/>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="13" t="inlineStr"/>
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Comfort Suites North</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>9620</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="11" t="inlineStr"/>
-      <c r="B16" s="12" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="13" t="inlineStr"/>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Corner Pocket Pub</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>9605</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>EX 200</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>EX200</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="11" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="13" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Crispy Cones</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>18449</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>EX 002</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="13" t="inlineStr"/>
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Curly's Village Inn</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>3027</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>EX200</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="11" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="13" t="inlineStr"/>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Curly's Village Inn</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>3027</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>Trap Size &amp; Units</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>20 gal</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>20 gpm</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="11" t="inlineStr"/>
-      <c r="B20" s="12" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="13" t="inlineStr"/>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Deer Park Irish Pub</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>9305</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>EX200</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="11" t="inlineStr"/>
-      <c r="B21" s="6" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="13" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Dicky's 21 Tap</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>4558</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Trap Size &amp; Units</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>20 gal</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>20 gpm</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="11" t="inlineStr"/>
-      <c r="B22" s="12" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="13" t="inlineStr"/>
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Domino's</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>18479</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>EX200</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="11" t="inlineStr"/>
-      <c r="B23" s="6" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="13" t="inlineStr"/>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Domino's</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>18479</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Trap Size &amp; Units</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>50 gal</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>50 gpm</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="11" t="inlineStr"/>
-      <c r="B24" s="12" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="13" t="inlineStr"/>
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Don Hall's Factory Restaurant</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>3608</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="11" t="inlineStr"/>
-      <c r="B25" s="12" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="13" t="inlineStr"/>
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Golden Corral</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>17407</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="11" t="inlineStr"/>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="13" t="inlineStr"/>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Hoshi Hoshi</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>18463</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="11" t="inlineStr"/>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="13" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Hoshi Hoshi</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>18463</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Trap Size &amp; Units</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>20 gal</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>20 gpm</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="11" t="inlineStr"/>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="13" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Hoshi Hoshi</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>18463</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Twice Monthly</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="11" t="inlineStr"/>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="13" t="inlineStr"/>
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Kim Thai Buffet</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>2909</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="11" t="inlineStr"/>
-      <c r="B30" s="12" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="13" t="inlineStr"/>
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>King Gyros</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>1533</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>three times weekly</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>Three Times Weekly</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="11" t="inlineStr"/>
-      <c r="B31" s="12" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="13" t="inlineStr"/>
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>La Cabana 2</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>18486</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>EX200</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="11" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="13" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>La Cabana 2</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>18486</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Trap Size &amp; Units</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>40 gal</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>40 gpm</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="11" t="inlineStr"/>
-      <c r="B33" s="6" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="13" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>La Santa Anita Family Grill</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>2346</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="11" t="inlineStr"/>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="13" t="inlineStr"/>
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>LaLos Restaurante Mexicano</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>17800</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>three times weekly</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>Three Times Weekly</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="11" t="inlineStr"/>
-      <c r="B35" s="12" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="13" t="inlineStr"/>
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Las Delicias Del Gordito</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>9495</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="11" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="13" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Legendary Life Bar</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>18450</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="11" t="inlineStr"/>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="13" t="inlineStr"/>
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>Lengerich Meats Inc.</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>17590</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="11" t="inlineStr"/>
-      <c r="B38" s="12" t="inlineStr">
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="13" t="inlineStr"/>
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>Life in Balance Nutrition</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>18461</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F42" s="14" t="inlineStr">
         <is>
           <t>EX200</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="11" t="inlineStr"/>
-      <c r="B39" s="12" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="13" t="inlineStr"/>
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>Los Cabos Mexican Grill</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>10315</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>three times weekly</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>Three Times Weekly</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="11" t="inlineStr"/>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="13" t="inlineStr"/>
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Loving Café</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>10195</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="11" t="inlineStr"/>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="13" t="inlineStr"/>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Mama Mia Pizza</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>6546</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Trap Size &amp; Units</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>25 gal</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>25 gpm</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="11" t="inlineStr"/>
-      <c r="B42" s="12" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="13" t="inlineStr"/>
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>Morgans Tap &amp; Grill</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>3081</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="11" t="inlineStr"/>
-      <c r="B43" s="12" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="13" t="inlineStr"/>
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>Mozzarelli's Pizza</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>9376</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F43" s="12" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>EX200</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="11" t="inlineStr"/>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="13" t="inlineStr"/>
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Mystic Arcade</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>18476</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="11" t="inlineStr"/>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="13" t="inlineStr"/>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Pepper &amp; Spice Jamaican Restaurant</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>17421</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>Trap Size &amp; Units</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>20 gal</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>20 gpm</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="11" t="inlineStr"/>
-      <c r="B46" s="12" t="inlineStr">
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="13" t="inlineStr"/>
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>Pizza King</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>5796</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>EX200</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="11" t="inlineStr"/>
-      <c r="B47" s="6" t="inlineStr">
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="13" t="inlineStr"/>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Pizza King</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>5796</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Trap Size &amp; Units</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>20 lbs</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>20 gpm</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="11" t="inlineStr"/>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="13" t="inlineStr"/>
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Real Alloy</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>18192</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>HSW - Station 1</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="11" t="inlineStr"/>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="13" t="inlineStr"/>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Real Alloy</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>18192</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E53" s="11" t="inlineStr">
         <is>
           <t>SEPTIC - Station 2</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="11" t="inlineStr"/>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="13" t="inlineStr"/>
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Salsa Grill Northeast</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>17583</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E54" s="11" t="inlineStr">
         <is>
           <t>EX900</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="11" t="inlineStr"/>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="13" t="inlineStr"/>
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>Sol De Mexico Bar &amp; Grill</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>10353</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E51" s="15" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>three times weekly</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>Three Times Weekly</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="11" t="inlineStr"/>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="13" t="inlineStr"/>
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>St. Paul's Lutheran - Heritage Hall</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>18404</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="11" t="inlineStr"/>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="13" t="inlineStr"/>
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>Storming Crab (CUGC)</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C57" s="15" t="inlineStr">
         <is>
           <t>6024</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F53" s="12" t="inlineStr">
+      <c r="F57" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="11" t="inlineStr"/>
-      <c r="B54" s="12" t="inlineStr">
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="13" t="inlineStr"/>
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>Subway #1141</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>0823</t>
         </is>
       </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F54" s="12" t="inlineStr">
+      <c r="F58" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="11" t="inlineStr"/>
-      <c r="B55" s="12" t="inlineStr">
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="13" t="inlineStr"/>
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>Taco Bell #36384</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C59" s="15" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="F59" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Report Name:</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>FSE Inspections – Last 5 Years</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Fields Checked:</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Receiving Plant,  Class Code,  Second Class,  Trunk Line</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Board &amp; Bond</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>18034</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="11" t="inlineStr"/>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="13" t="inlineStr"/>
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>17732</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Class Code</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>Distillery (No Food)</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F64" s="14" t="inlineStr">
         <is>
           <t>Distillery (No food)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="11" t="inlineStr"/>
-      <c r="B61" s="6" t="inlineStr">
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="13" t="inlineStr"/>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Cooking With Herbs Catering LLC</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>18388</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D65" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E65" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="11" t="inlineStr"/>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="13" t="inlineStr"/>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Dupont Sports and Medicine Complex</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>17939</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>Trunk Line</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>.</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr"/>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="11" t="inlineStr"/>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="13" t="inlineStr"/>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>El Rey del Pincho FT</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>18274</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="11" t="inlineStr"/>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="13" t="inlineStr"/>
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Gratitude Catering</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>17779</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="11" t="inlineStr"/>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="13" t="inlineStr"/>
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>Hatfield &amp; Sons Distillery</t>
         </is>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>18157</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>Class Code</t>
         </is>
       </c>
-      <c r="E65" s="15" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>Distillery (No Food)</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>Distillery (No food)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="11" t="inlineStr"/>
-      <c r="B66" s="12" t="inlineStr">
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="13" t="inlineStr"/>
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>Let's Get Nailed</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>17971</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>Class Code</t>
         </is>
       </c>
-      <c r="E66" s="15" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>Salon (No Food)</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="F70" s="14" t="inlineStr">
         <is>
           <t>Salon (No food)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="11" t="inlineStr"/>
-      <c r="B67" s="12" t="inlineStr">
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="13" t="inlineStr"/>
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>M. Vince Nail Spa</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>17861</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>Class Code</t>
         </is>
       </c>
-      <c r="E67" s="15" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>Salon (No Food)</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="F71" s="14" t="inlineStr">
         <is>
           <t>Salon (No food)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="11" t="inlineStr"/>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="13" t="inlineStr"/>
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>Majestic Care</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>9922</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="11" t="inlineStr"/>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="13" t="inlineStr"/>
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>Queen Nails</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>18400</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>Class Code</t>
         </is>
       </c>
-      <c r="E69" s="15" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>Salon (No Food)</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="F73" s="14" t="inlineStr">
         <is>
           <t>Salon (No food)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="11" t="inlineStr"/>
-      <c r="B70" s="12" t="inlineStr">
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="13" t="inlineStr"/>
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>Royalty Nails Lounge</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C74" s="15" t="inlineStr">
         <is>
           <t>17765</t>
         </is>
       </c>
-      <c r="D70" s="14" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>Class Code</t>
         </is>
       </c>
-      <c r="E70" s="15" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>Salon (No Food)</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="F74" s="14" t="inlineStr">
         <is>
           <t>Salon (No food)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="11" t="inlineStr"/>
-      <c r="B71" s="6" t="inlineStr">
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="13" t="inlineStr"/>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Taco Rancho Grande</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>18036</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="11" t="inlineStr"/>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="13" t="inlineStr"/>
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>The Flavor Patch FT</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>18287</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="E76" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="11" t="inlineStr"/>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="13" t="inlineStr"/>
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>Tiffany Nails Inc.</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C77" s="15" t="inlineStr">
         <is>
           <t>17657</t>
         </is>
       </c>
-      <c r="D73" s="14" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>Class Code</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="E77" s="17" t="inlineStr">
         <is>
           <t>Salon (No Food)</t>
         </is>
       </c>
-      <c r="F73" s="12" t="inlineStr">
+      <c r="F77" s="14" t="inlineStr">
         <is>
           <t>Salon (No food)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="11" t="inlineStr"/>
-      <c r="B74" s="6" t="inlineStr">
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="13" t="inlineStr"/>
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Tocho Snack Bar</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>18018</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E74" s="9" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="11" t="inlineStr"/>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="13" t="inlineStr"/>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Ziano's</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>9973</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D79" s="10" t="inlineStr">
         <is>
           <t>Receiving Plant</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E79" s="11" t="inlineStr">
         <is>
           <t>Aqua Indiana</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Report Name:</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Master List with Additional Fields</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>Fields Checked:</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Clean City Bins</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>18181</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D83" s="10" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
+      <c r="E83" s="11" t="inlineStr">
         <is>
           <t>Quasar</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="11" t="inlineStr"/>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="13" t="inlineStr"/>
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Dannon Co.</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>18460</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>Quasar</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="11" t="inlineStr"/>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="13" t="inlineStr"/>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Divert Inc.</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>18186</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D85" s="10" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="E85" s="11" t="inlineStr">
         <is>
           <t>Quasar</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="11" t="inlineStr"/>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="13" t="inlineStr"/>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Drumm Inc.</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>17817</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t>Quasar</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="11" t="inlineStr"/>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="13" t="inlineStr"/>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Emery</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>17849</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
-      <c r="E83" s="9" t="inlineStr">
+      <c r="E87" s="11" t="inlineStr">
         <is>
           <t>Quasar</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="11" t="inlineStr"/>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="13" t="inlineStr"/>
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Nestle</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>17459</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="E88" s="11" t="inlineStr">
         <is>
           <t>Quasar</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="11" t="inlineStr"/>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="13" t="inlineStr"/>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Proctor &amp; Gamble Lima</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>17848</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr">
+      <c r="E89" s="11" t="inlineStr">
         <is>
           <t>Quasar</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>Report Name:</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>AG Extract Summary</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>Fields Checked:</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Extractor ID,  Extractor Type</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>Report Name:</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Inspection Events</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>Fields Checked:</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>Allen County Community Corrections Residential Services Facillity</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>17854</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D97" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E93" s="9" t="inlineStr">
+      <c r="E97" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="11" t="inlineStr"/>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="13" t="inlineStr"/>
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>Bubba's 33</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C98" s="9" t="inlineStr">
         <is>
           <t>18459</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="D98" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr">
+      <c r="E98" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="11" t="inlineStr"/>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="13" t="inlineStr"/>
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>Crispy Cones</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>18449</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D99" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
+      <c r="E99" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="11" t="inlineStr"/>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="13" t="inlineStr"/>
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>Drive &amp; Shine Car Wash</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>18465</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D100" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E100" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="11" t="inlineStr"/>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="13" t="inlineStr"/>
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>Drive &amp; Shine Lube Center</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>18467</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E97" s="9" t="inlineStr">
+      <c r="E101" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="11" t="inlineStr"/>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="13" t="inlineStr"/>
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>Dunkin Donuts #346590</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C102" s="9" t="inlineStr">
         <is>
           <t>10211</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="E102" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F98" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="11" t="inlineStr"/>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="13" t="inlineStr"/>
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Headwaters Church</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C103" s="9" t="inlineStr">
         <is>
           <t>9392</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="E103" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="11" t="inlineStr"/>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="13" t="inlineStr"/>
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>Hoshi Hoshi</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>18463</t>
         </is>
       </c>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="D104" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E100" s="9" t="inlineStr">
+      <c r="E104" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="11" t="inlineStr"/>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="13" t="inlineStr"/>
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>Mi Tierra Market</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>18458</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E101" s="9" t="inlineStr">
+      <c r="E105" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="11" t="inlineStr"/>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="13" t="inlineStr"/>
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>Rise N Roll Bakery &amp; Deli</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C106" s="9" t="inlineStr">
         <is>
           <t>0067</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="E106" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="11" t="inlineStr"/>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="13" t="inlineStr"/>
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>Thai Diner Restaurant</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>1259</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D107" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E103" s="9" t="inlineStr">
+      <c r="E107" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="11" t="inlineStr"/>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="13" t="inlineStr"/>
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>The Grind</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>9777</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="E108" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F104" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="11" t="inlineStr"/>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="13" t="inlineStr"/>
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>Valvoline</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>18423</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D109" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E105" s="9" t="inlineStr">
+      <c r="E109" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="11" t="inlineStr"/>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="13" t="inlineStr"/>
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>Van Eerden Food Service</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C110" s="9" t="inlineStr">
         <is>
           <t>18441</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E106" s="9" t="inlineStr">
+      <c r="E110" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="11" t="inlineStr"/>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="13" t="inlineStr"/>
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>Wing Stop</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="C111" s="9" t="inlineStr">
         <is>
           <t>17897</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D111" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E107" s="9" t="inlineStr">
+      <c r="E111" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="11" t="inlineStr"/>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="13" t="inlineStr"/>
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>YWCA/Gratitude Catering</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C112" s="9" t="inlineStr">
         <is>
           <t>9269</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr">
+      <c r="D112" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="E112" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F108" s="10" t="inlineStr">
+      <c r="F112" s="12" t="inlineStr">
         <is>
           <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="C4:F4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
+++ b/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2109,138 +2109,66 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1">
+    <row r="63" ht="16" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Board &amp; Bond</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>18034</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>Receiving Plant</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>Aqua Indiana</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="13" t="inlineStr"/>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>17732</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>Class Code</t>
-        </is>
-      </c>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>Distillery (No Food)</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>Distillery (No food)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="13" t="inlineStr"/>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>Cooking With Herbs Catering LLC</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>18388</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>Receiving Plant</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>Aqua Indiana</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="13" t="inlineStr"/>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Dupont Sports and Medicine Complex</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>17939</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>Trunk Line</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Report Name:</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Master List with Additional Fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Fields Checked:</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Map Category</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="13" t="inlineStr"/>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Issues Found:</t>
+        </is>
+      </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>El Rey del Pincho FT</t>
+          <t>Clean City Bins</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Receiving Plant</t>
+          <t>Map Category</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Aqua Indiana</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -2253,22 +2181,22 @@
       <c r="A68" s="13" t="inlineStr"/>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Gratitude Catering</t>
+          <t>Dannon Co.</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Receiving Plant</t>
+          <t>Map Category</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Aqua Indiana</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -2279,85 +2207,85 @@
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="13" t="inlineStr"/>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>Hatfield &amp; Sons Distillery</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>18157</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="inlineStr">
-        <is>
-          <t>Class Code</t>
-        </is>
-      </c>
-      <c r="E69" s="17" t="inlineStr">
-        <is>
-          <t>Distillery (No Food)</t>
-        </is>
-      </c>
-      <c r="F69" s="14" t="inlineStr">
-        <is>
-          <t>Distillery (No food)</t>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Divert Inc.</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>18186</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Map Category</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Quasar</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="13" t="inlineStr"/>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>Let's Get Nailed</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
-        <is>
-          <t>17971</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>Class Code</t>
-        </is>
-      </c>
-      <c r="E70" s="17" t="inlineStr">
-        <is>
-          <t>Salon (No Food)</t>
-        </is>
-      </c>
-      <c r="F70" s="14" t="inlineStr">
-        <is>
-          <t>Salon (No food)</t>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Drumm Inc.</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>17817</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Map Category</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>Quasar</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="13" t="inlineStr"/>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>M. Vince Nail Spa</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>17861</t>
-        </is>
-      </c>
-      <c r="D71" s="16" t="inlineStr">
-        <is>
-          <t>Class Code</t>
-        </is>
-      </c>
-      <c r="E71" s="17" t="inlineStr">
-        <is>
-          <t>Salon (No Food)</t>
-        </is>
-      </c>
-      <c r="F71" s="14" t="inlineStr">
-        <is>
-          <t>Salon (No food)</t>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Emery</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>17849</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Map Category</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Quasar</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
@@ -2365,22 +2293,22 @@
       <c r="A72" s="13" t="inlineStr"/>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Majestic Care</t>
+          <t>Nestle</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Receiving Plant</t>
+          <t>Map Category</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Aqua Indiana</t>
+          <t>Quasar</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -2391,248 +2319,172 @@
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="13" t="inlineStr"/>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>Queen Nails</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t>18400</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="inlineStr">
-        <is>
-          <t>Class Code</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
-        <is>
-          <t>Salon (No Food)</t>
-        </is>
-      </c>
-      <c r="F73" s="14" t="inlineStr">
-        <is>
-          <t>Salon (No food)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="13" t="inlineStr"/>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>Royalty Nails Lounge</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>17765</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>Class Code</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>Salon (No Food)</t>
-        </is>
-      </c>
-      <c r="F74" s="14" t="inlineStr">
-        <is>
-          <t>Salon (No food)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="13" t="inlineStr"/>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Taco Rancho Grande</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>18036</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>Receiving Plant</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>Aqua Indiana</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="13" t="inlineStr"/>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>The Flavor Patch FT</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>18287</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Receiving Plant</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>Aqua Indiana</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="13" t="inlineStr"/>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>Tiffany Nails Inc.</t>
-        </is>
-      </c>
-      <c r="C77" s="15" t="inlineStr">
-        <is>
-          <t>17657</t>
-        </is>
-      </c>
-      <c r="D77" s="16" t="inlineStr">
-        <is>
-          <t>Class Code</t>
-        </is>
-      </c>
-      <c r="E77" s="17" t="inlineStr">
-        <is>
-          <t>Salon (No Food)</t>
-        </is>
-      </c>
-      <c r="F77" s="14" t="inlineStr">
-        <is>
-          <t>Salon (No food)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="13" t="inlineStr"/>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Tocho Snack Bar</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>18018</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>Receiving Plant</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>Aqua Indiana</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="13" t="inlineStr"/>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Ziano's</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>9973</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>Receiving Plant</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>Aqua Indiana</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Proctor &amp; Gamble Lima</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>17848</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Map Category</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Quasar</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Report Name:</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>AG Extract Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Fields Checked:</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Extractor ID,  Extractor Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Issues Found:</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Report Name:</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Inspection Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Fields Checked:</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Event Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Report Name:</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Master List with Additional Fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Fields Checked:</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Map Category</t>
+          <t>Issues Found:</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Allen County Community Corrections Residential Services Facillity</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>17854</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Event Type</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="13" t="inlineStr"/>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Bubba's 33</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>18459</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Event Type</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Issues Found:</t>
-        </is>
-      </c>
+      <c r="A83" s="13" t="inlineStr"/>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Clean City Bins</t>
+          <t>Crispy Cones</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Map Category</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Quasar</t>
+          <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -2645,22 +2497,22 @@
       <c r="A84" s="13" t="inlineStr"/>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Dannon Co.</t>
+          <t>Drive &amp; Shine Car Wash</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>18460</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Map Category</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Quasar</t>
+          <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
@@ -2673,22 +2525,22 @@
       <c r="A85" s="13" t="inlineStr"/>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Divert Inc.</t>
+          <t>Drive &amp; Shine Lube Center</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>18186</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Map Category</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Quasar</t>
+          <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -2701,22 +2553,22 @@
       <c r="A86" s="13" t="inlineStr"/>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Drumm Inc.</t>
+          <t>Dunkin Donuts #346590</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>17817</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Map Category</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Quasar</t>
+          <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
@@ -2729,22 +2581,22 @@
       <c r="A87" s="13" t="inlineStr"/>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Emery</t>
+          <t>Headwaters Church</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Map Category</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Quasar</t>
+          <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -2757,22 +2609,22 @@
       <c r="A88" s="13" t="inlineStr"/>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Nestle</t>
+          <t>Hoshi Hoshi</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Map Category</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Quasar</t>
+          <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
@@ -2785,22 +2637,22 @@
       <c r="A89" s="13" t="inlineStr"/>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>Proctor &amp; Gamble Lima</t>
+          <t>Mi Tierra Market</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Map Category</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Quasar</t>
+          <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -2809,513 +2661,197 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>Report Name:</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>AG Extract Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>Fields Checked:</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Extractor ID,  Extractor Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>Issues Found:</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>Report Name:</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Inspection Events</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Fields Checked:</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="13" t="inlineStr"/>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Rise N Roll Bakery &amp; Deli</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>0067</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Issues Found:</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Allen County Community Corrections Residential Services Facillity</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>17854</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>Dye Trace Monitoring Point</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="13" t="inlineStr"/>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Thai Diner Restaurant</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E97" s="11" t="inlineStr">
+      <c r="E91" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F97" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="13" t="inlineStr"/>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Bubba's 33</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>18459</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="inlineStr">
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="13" t="inlineStr"/>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>The Grind</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>9777</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E98" s="11" t="inlineStr">
+      <c r="E92" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F98" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="13" t="inlineStr"/>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Crispy Cones</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="13" t="inlineStr"/>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Valvoline</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>18423</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E99" s="11" t="inlineStr">
+      <c r="E93" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F99" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="13" t="inlineStr"/>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Drive &amp; Shine Car Wash</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="13" t="inlineStr"/>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Van Eerden Food Service</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>18441</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E100" s="11" t="inlineStr">
+      <c r="E94" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F100" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="13" t="inlineStr"/>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>Drive &amp; Shine Lube Center</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>18467</t>
-        </is>
-      </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="13" t="inlineStr"/>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Wing Stop</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>17897</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E101" s="11" t="inlineStr">
+      <c r="E95" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F101" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="13" t="inlineStr"/>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Dunkin Donuts #346590</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>10211</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="13" t="inlineStr"/>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>YWCA/Gratitude Catering</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>9269</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="E102" s="11" t="inlineStr">
+      <c r="E96" s="11" t="inlineStr">
         <is>
           <t>Dye Trace Monitoring Point</t>
         </is>
       </c>
-      <c r="F102" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="13" t="inlineStr"/>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Headwaters Church</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>9392</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F103" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="13" t="inlineStr"/>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Hoshi Hoshi</t>
-        </is>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>18463</t>
-        </is>
-      </c>
-      <c r="D104" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E104" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F104" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="13" t="inlineStr"/>
-      <c r="B105" s="8" t="inlineStr">
-        <is>
-          <t>Mi Tierra Market</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>18458</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F105" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="13" t="inlineStr"/>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>Rise N Roll Bakery &amp; Deli</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>0067</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E106" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F106" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="13" t="inlineStr"/>
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>Thai Diner Restaurant</t>
-        </is>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="D107" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="13" t="inlineStr"/>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>The Grind</t>
-        </is>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>9777</t>
-        </is>
-      </c>
-      <c r="D108" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F108" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="13" t="inlineStr"/>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Valvoline</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>18423</t>
-        </is>
-      </c>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="13" t="inlineStr"/>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Van Eerden Food Service</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>18441</t>
-        </is>
-      </c>
-      <c r="D110" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F110" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="13" t="inlineStr"/>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>Wing Stop</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>17897</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F111" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="13" t="inlineStr"/>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>YWCA/Gratitude Catering</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>9269</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E112" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F112" s="12" t="inlineStr">
+      <c r="F96" s="12" t="inlineStr">
         <is>
           <t>Needs Manual Review</t>
         </is>

--- a/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
+++ b/LinkoDB_Monthly_Cleanup_Script/output/Monthly_Quality_Check_Report.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -633,22 +633,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>American Kolache</t>
+          <t>07 Pub</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Extractor Type</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>SIDEWAYS-FLOOR</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -659,29 +659,29 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="13" t="inlineStr"/>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Arby's #1201</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>6052</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Cleaning Frequency</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Every 2 months</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>Every 2 Months</t>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>07 Pub</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Trap Size &amp; Units</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>35 gal</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>35 gpm</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       <c r="A10" s="13" t="inlineStr"/>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>B. Antonio's Pizza</t>
+          <t>19th Hole</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>EX999</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -717,27 +717,27 @@
       <c r="A11" s="13" t="inlineStr"/>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Bowen Coffee Shop</t>
+          <t>19th Hole</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Extractor Type</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>in-floor</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>EX120</t>
+          <t>IN-FLOOR</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       <c r="A12" s="13" t="inlineStr"/>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Buffalo Wild Wings</t>
+          <t>19th Hole</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>Every 2 months</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Every 2 Months</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       <c r="A13" s="13" t="inlineStr"/>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Burger Bar</t>
+          <t>American Kolache</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>18443</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>050</t>
+          <t>001</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -801,12 +801,12 @@
       <c r="A14" s="13" t="inlineStr"/>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Chick-fil-A #03479</t>
+          <t>Arby's #1201</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -827,29 +827,29 @@
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="13" t="inlineStr"/>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Chicken Salad Chick</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>18130</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>Cleaning Frequency</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>Every 2 months</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>Every 2 Months</t>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>B. Antonio's Pizza</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>9893</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Extractor ID</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       <c r="A16" s="13" t="inlineStr"/>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>Bowen Coffee Shop</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>Cleaning Frequency</t>
+          <t>Extractor ID</t>
         </is>
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>Every 2 months</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Every 2 Months</t>
+          <t>EX120</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       <c r="A17" s="13" t="inlineStr"/>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>Buffalo Wild Wings</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
@@ -913,12 +913,12 @@
       <c r="A18" s="13" t="inlineStr"/>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Club Soda</t>
+          <t>Burger Bar</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>EX001</t>
+          <t>050</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -941,12 +941,12 @@
       <c r="A19" s="13" t="inlineStr"/>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Comfort Suites North</t>
+          <t>Chick-fil-A #03479</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
@@ -969,55 +969,55 @@
       <c r="A20" s="13" t="inlineStr"/>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Corner Pocket Pub</t>
+          <t>Chicken Salad Chick</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Cleaning Frequency</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>EX 200</t>
+          <t>Every 2 months</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>EX200</t>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="13" t="inlineStr"/>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Crispy Cones</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Extractor ID</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>EX 002</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>9322</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Cleaning Frequency</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Every 2 months</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
@@ -1025,27 +1025,27 @@
       <c r="A22" s="13" t="inlineStr"/>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Curly's Village Inn</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Cleaning Frequency</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Every 2 months</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>EX200</t>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
@@ -1053,27 +1053,27 @@
       <c r="A23" s="13" t="inlineStr"/>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Curly's Village Inn</t>
+          <t>Club Soda</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Trap Size &amp; Units</t>
+          <t>Extractor ID</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>20 gal</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>20 gpm</t>
+          <t>EX001</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
@@ -1081,139 +1081,139 @@
       <c r="A24" s="13" t="inlineStr"/>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Deer Park Irish Pub</t>
+          <t>Comfort Suites North</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Cleaning Frequency</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Every 2 months</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>EX200</t>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="13" t="inlineStr"/>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Dicky's 21 Tap</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>4558</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Trap Size &amp; Units</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>20 gal</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>20 gpm</t>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Corner Pocket Pub</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>9605</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Extractor ID</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>EX 200</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>EX200</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="13" t="inlineStr"/>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Domino's</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>18479</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Crispy Cones</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>18449</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>EX200</t>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>EX 002</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="13" t="inlineStr"/>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Domino's</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>18479</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Trap Size &amp; Units</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>50 gal</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>50 gpm</t>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Curly's Village Inn</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>3027</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Extractor ID</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>EX200</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="13" t="inlineStr"/>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Don Hall's Factory Restaurant</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>3608</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>Cleaning Frequency</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>Every 2 months</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Every 2 Months</t>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Curly's Village Inn</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>3027</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Trap Size &amp; Units</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>20 gal</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>20 gpm</t>
         </is>
       </c>
     </row>
@@ -1221,27 +1221,27 @@
       <c r="A29" s="13" t="inlineStr"/>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Golden Corral</t>
+          <t>Deer Park Irish Pub</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>Cleaning Frequency</t>
+          <t>Extractor ID</t>
         </is>
       </c>
       <c r="E29" s="17" t="inlineStr">
         <is>
-          <t>Every 2 months</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Every 2 Months</t>
+          <t>EX200</t>
         </is>
       </c>
     </row>
@@ -1249,55 +1249,55 @@
       <c r="A30" s="13" t="inlineStr"/>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Hoshi Hoshi</t>
+          <t>Dicky's 21 Tap</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Trap Size &amp; Units</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+          <t>20 gal</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>20 gpm</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="13" t="inlineStr"/>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Hoshi Hoshi</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>18463</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Trap Size &amp; Units</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>20 gal</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>20 gpm</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Domino's</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>18479</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Extractor ID</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>EX200</t>
         </is>
       </c>
     </row>
@@ -1305,27 +1305,27 @@
       <c r="A32" s="13" t="inlineStr"/>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Hoshi Hoshi</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Cleaning Frequency</t>
+          <t>Trap Size &amp; Units</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Twice Monthly</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+          <t>50 gal</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>50 gpm</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       <c r="A33" s="13" t="inlineStr"/>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Kim Thai Buffet</t>
+          <t>Don Hall's Factory Restaurant</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
@@ -1361,12 +1361,12 @@
       <c r="A34" s="13" t="inlineStr"/>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>King Gyros</t>
+          <t>Golden Corral</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
@@ -1376,40 +1376,40 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>three times weekly</t>
+          <t>Every 2 months</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Three Times Weekly</t>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="13" t="inlineStr"/>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>La Cabana 2</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>18486</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Hoshi Hoshi</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>18463</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>EX200</t>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       <c r="A36" s="13" t="inlineStr"/>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>La Cabana 2</t>
+          <t>Hoshi Hoshi</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>18486</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>40 gal</t>
+          <t>20 gal</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>40 gpm</t>
+          <t>20 gpm</t>
         </is>
       </c>
     </row>
@@ -1445,22 +1445,22 @@
       <c r="A37" s="13" t="inlineStr"/>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>La Santa Anita Family Grill</t>
+          <t>Hoshi Hoshi</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Cleaning Frequency</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>Twice Monthly</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -1473,12 +1473,12 @@
       <c r="A38" s="13" t="inlineStr"/>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>LaLos Restaurante Mexicano</t>
+          <t>Kim Thai Buffet</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>three times weekly</t>
+          <t>Every 2 months</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Three Times Weekly</t>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       <c r="A39" s="13" t="inlineStr"/>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Las Delicias Del Gordito</t>
+          <t>King Gyros</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
@@ -1516,96 +1516,96 @@
       </c>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>Every 2 months</t>
+          <t>three times weekly</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Every 2 Months</t>
+          <t>Three Times Weekly</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="13" t="inlineStr"/>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Legendary Life Bar</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>18450</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>La Cabana 2</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>18486</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>EX200</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="13" t="inlineStr"/>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>Lengerich Meats Inc.</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>17590</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>Cleaning Frequency</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>Every 2 months</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>Every 2 Months</t>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>La Cabana 2</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>18486</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Trap Size &amp; Units</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>40 gal</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>40 gpm</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="13" t="inlineStr"/>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>Life in Balance Nutrition</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>18461</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>La Santa Anita Family Grill</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>2346</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>EX200</t>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       <c r="A43" s="13" t="inlineStr"/>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Los Cabos Mexican Grill</t>
+          <t>LaLos Restaurante Mexicano</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
@@ -1639,29 +1639,29 @@
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="13" t="inlineStr"/>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Loving Café</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>10195</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Extractor ID</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Las Delicias Del Gordito</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>9495</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Cleaning Frequency</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>Every 2 months</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
@@ -1669,27 +1669,27 @@
       <c r="A45" s="13" t="inlineStr"/>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>Mama Mia Pizza</t>
+          <t>Legendary Life Bar</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Trap Size &amp; Units</t>
+          <t>Extractor ID</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>25 gal</t>
-        </is>
-      </c>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>25 gpm</t>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       <c r="A46" s="13" t="inlineStr"/>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Morgans Tap &amp; Grill</t>
+          <t>Lengerich Meats Inc.</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -1725,12 +1725,12 @@
       <c r="A47" s="13" t="inlineStr"/>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Mozzarelli's Pizza</t>
+          <t>Life in Balance Nutrition</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
@@ -1751,29 +1751,29 @@
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="13" t="inlineStr"/>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Mystic Arcade</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>18476</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>Extractor ID</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Los Cabos Mexican Grill</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>10315</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>Cleaning Frequency</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>three times weekly</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Three Times Weekly</t>
         </is>
       </c>
     </row>
@@ -1781,111 +1781,111 @@
       <c r="A49" s="13" t="inlineStr"/>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Pepper &amp; Spice Jamaican Restaurant</t>
+          <t>Loving Café</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Trap Size &amp; Units</t>
+          <t>Extractor ID</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>20 gal</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>20 gpm</t>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="13" t="inlineStr"/>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>Pizza King</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>5796</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>Extractor ID</t>
-        </is>
-      </c>
-      <c r="E50" s="17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>EX200</t>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Mama Mia Pizza</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>6546</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Trap Size &amp; Units</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>25 gal</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>25 gpm</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="13" t="inlineStr"/>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Pizza King</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>5796</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>Trap Size &amp; Units</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>20 lbs</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>20 gpm</t>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Morgans Tap &amp; Grill</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Cleaning Frequency</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>Every 2 months</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>Every 2 Months</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="13" t="inlineStr"/>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Real Alloy</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>18192</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Mozzarelli's Pizza</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>9376</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Extractor ID</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>HSW - Station 1</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>EX200</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       <c r="A53" s="13" t="inlineStr"/>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Real Alloy</t>
+          <t>Mystic Arcade</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>SEPTIC - Station 2</t>
+          <t>001</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -1921,27 +1921,27 @@
       <c r="A54" s="13" t="inlineStr"/>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Salsa Grill Northeast</t>
+          <t>Pepper &amp; Spice Jamaican Restaurant</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>17583</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Trap Size &amp; Units</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>EX900</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+          <t>20 gal</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>20 gpm</t>
         </is>
       </c>
     </row>
@@ -1949,27 +1949,27 @@
       <c r="A55" s="13" t="inlineStr"/>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Sol De Mexico Bar &amp; Grill</t>
+          <t>Pizza King</t>
         </is>
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Cleaning Frequency</t>
+          <t>Extractor ID</t>
         </is>
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>three times weekly</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>Three Times Weekly</t>
+          <t>EX200</t>
         </is>
       </c>
     </row>
@@ -1977,883 +1977,395 @@
       <c r="A56" s="13" t="inlineStr"/>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>St. Paul's Lutheran - Heritage Hall</t>
+          <t>Pizza King</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Extractor ID</t>
+          <t>Trap Size &amp; Units</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+          <t>20 lbs</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>20 gpm</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="13" t="inlineStr"/>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>Storming Crab (CUGC)</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>Cleaning Frequency</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>Every 2 months</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>Every 2 Months</t>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Real Alloy</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>18192</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Extractor ID</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>HSW - Station 1</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="13" t="inlineStr"/>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>Subway #1141</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>0823</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>Cleaning Frequency</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>Every 2 months</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
-        <is>
-          <t>Every 2 Months</t>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Real Alloy</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>18192</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Extractor ID</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>SEPTIC - Station 2</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="13" t="inlineStr"/>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Salsa Grill Northeast</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>17583</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Extractor ID</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>EX900</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="13" t="inlineStr"/>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Sol De Mexico Bar &amp; Grill</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>10353</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>Cleaning Frequency</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>three times weekly</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>Three Times Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="13" t="inlineStr"/>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>St. Paul's Lutheran - Heritage Hall</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>18404</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Extractor ID</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>Needs Manual Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="13" t="inlineStr"/>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Storming Crab (CUGC)</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>Cleaning Frequency</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Every 2 months</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>Every 2 Months</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="13" t="inlineStr"/>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Subway #1141</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>0823</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>Cleaning Frequency</t>
+        </is>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>Every 2 months</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>Every 2 Months</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="13" t="inlineStr"/>
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>Taco Bell #36384</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Cleaning Frequency</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>Every 2 months</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F64" s="14" t="inlineStr">
         <is>
           <t>Every 2 Months</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Report Name:</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>FSE Inspections – Last 5 Years</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Fields Checked:</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Receiving Plant,  Class Code,  Second Class,  Trunk Line</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>Report Name:</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Master List with Additional Fields</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Fields Checked:</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Map Category</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Issues Found:</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Clean City Bins</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>18181</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>Map Category</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>Quasar</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="13" t="inlineStr"/>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Dannon Co.</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>18460</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Map Category</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>Quasar</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="13" t="inlineStr"/>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Divert Inc.</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>18186</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Map Category</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>Quasar</t>
-        </is>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="13" t="inlineStr"/>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Drumm Inc.</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>17817</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>Map Category</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>Quasar</t>
-        </is>
-      </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="13" t="inlineStr"/>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Emery</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>17849</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>Map Category</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>Quasar</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="13" t="inlineStr"/>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Nestle</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>17459</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>Map Category</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>Quasar</t>
-        </is>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="13" t="inlineStr"/>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Proctor &amp; Gamble Lima</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>17848</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>Map Category</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>Quasar</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Report Name:</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>AG Extract Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Report Name:</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>AG Extract Summary</t>
+          <t>Fields Checked:</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Extractor ID,  Extractor Type</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
+          <t>Issues Found:</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Report Name:</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Inspection Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
           <t>Fields Checked:</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Extractor ID,  Extractor Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Issues Found:</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Report Name:</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Inspection Events</t>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Event Type</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Fields Checked:</t>
+          <t>Issues Found:</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Issues Found:</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Allen County Community Corrections Residential Services Facillity</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>17854</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="13" t="inlineStr"/>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Bubba's 33</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>18459</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="13" t="inlineStr"/>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Crispy Cones</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="13" t="inlineStr"/>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Drive &amp; Shine Car Wash</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="13" t="inlineStr"/>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>Drive &amp; Shine Lube Center</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>18467</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="13" t="inlineStr"/>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Dunkin Donuts #346590</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>10211</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="13" t="inlineStr"/>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Headwaters Church</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>9392</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="13" t="inlineStr"/>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Hoshi Hoshi</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>18463</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E88" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F88" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="13" t="inlineStr"/>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Mi Tierra Market</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>18458</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="13" t="inlineStr"/>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Rise N Roll Bakery &amp; Deli</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>0067</t>
-        </is>
-      </c>
-      <c r="D90" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="13" t="inlineStr"/>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Thai Diner Restaurant</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="13" t="inlineStr"/>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>The Grind</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>9777</t>
-        </is>
-      </c>
-      <c r="D92" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="13" t="inlineStr"/>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Valvoline</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>18423</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F93" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="13" t="inlineStr"/>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Van Eerden Food Service</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>18441</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F94" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="13" t="inlineStr"/>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Wing Stop</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>17897</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F95" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="13" t="inlineStr"/>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>YWCA/Gratitude Catering</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>9269</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>Dye Trace Monitoring Point</t>
-        </is>
-      </c>
-      <c r="F96" s="12" t="inlineStr">
-        <is>
-          <t>Needs Manual Review</t>
+          <t>None</t>
         </is>
       </c>
     </row>
